--- a/naver-place-crawler/results_health/부산_헬스장.xlsx
+++ b/naver-place-crawler/results_health/부산_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -427,7 +427,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="47" customWidth="1" min="8" max="8"/>
+    <col width="41" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -628,10 +628,10 @@
         <v>134</v>
       </c>
       <c r="Q2" t="n">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="R2" t="n">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -662,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>위헬스 장산역점</t>
+          <t>피트니스스퀘어 헬스&amp;PT&amp;기구필라테스 서면점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>wehealthjangsan@naver.com</t>
+          <t>fmpt__teddy@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1800-8273</t>
+          <t>0507-1343-6817</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산 해운대구 세실로 45 2층</t>
+          <t>부산 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://smartstore.naver.com/wehealth_jangsan</t>
+          <t>https://open.kakao.com/o/sksoe31e</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -709,12 +709,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5y91v</t>
+          <t>https://talk.naver.com/ct/w4fpwi</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>230</v>
+        <v>1089</v>
       </c>
       <c r="Q3" t="n">
-        <v>537</v>
+        <v>838</v>
       </c>
       <c r="R3" t="n">
-        <v>767</v>
+        <v>1927</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,51 +738,51 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1867376356</t>
+          <t>1138689357</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1867376356</t>
+          <t>https://m.place.naver.com/place/1138689357</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>피트니스스퀘어 헬스&amp;PT&amp;기구필라테스 서면점</t>
+          <t>플로우휘트니스 명지오션시티점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>fmpt__teddy@naver.com</t>
+          <t>j1024up@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1343-6817</t>
+          <t>0507-1491-2401</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
+          <t>부산 강서구 명지오션시티4로 90 6층 601호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sksoe31e</t>
+          <t>https://naver.me/5ISWRulS</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -802,32 +802,28 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4fpwi</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1086</v>
+        <v>42</v>
       </c>
       <c r="Q4" t="n">
-        <v>817</v>
+        <v>258</v>
       </c>
       <c r="R4" t="n">
-        <v>1903</v>
+        <v>300</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +832,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1138689357</t>
+          <t>1677475057</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1138689357</t>
+          <t>https://m.place.naver.com/place/1677475057</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -919,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1416</v>
+        <v>1422</v>
       </c>
       <c r="Q5" t="n">
-        <v>1516</v>
+        <v>1520</v>
       </c>
       <c r="R5" t="n">
-        <v>2932</v>
+        <v>2942</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -944,7 +940,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1017,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1451</v>
+        <v>1456</v>
       </c>
       <c r="Q6" t="n">
-        <v>1812</v>
+        <v>1825</v>
       </c>
       <c r="R6" t="n">
-        <v>3263</v>
+        <v>3281</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1042,7 +1038,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1054,34 +1050,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>스카이짐24H &amp; 기구필라테스 &amp; GDR골프</t>
+          <t>건담짐 미국감성프리미엄헬스&amp;PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>skygym21@naver.com</t>
+          <t>rlarjsdn12433@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1473-5661</t>
+          <t>0507-1323-5243</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산 사하구 장평로 440 5층</t>
+          <t>부산 동래구 온천천로 391 1층 건담짐</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://www.skygym.co.kr</t>
+          <t>https://blog.naver.com/rlarjsdn12433</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1101,7 +1097,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wqbu4w7</t>
+          <t>https://talk.naver.com/ct/w44x8o</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1111,17 +1107,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2075</v>
+        <v>2883</v>
       </c>
       <c r="Q7" t="n">
-        <v>137</v>
+        <v>900</v>
       </c>
       <c r="R7" t="n">
-        <v>2212</v>
+        <v>3783</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,17 +1126,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1429668350</t>
+          <t>1130935293</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1429668350</t>
+          <t>https://m.place.naver.com/place/1130935293</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1152,24 +1148,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>스카이짐24H &amp; 기구필라테스</t>
+          <t>스카이짐24H &amp; 기구필라테스 &amp; GDR골프</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>roadlife88@naver.com</t>
+          <t>skygym21@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1483-5661</t>
+          <t>0507-1473-5661</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산 동래구 안남로 108 화성코아 2층</t>
+          <t>부산 사하구 장평로 440 5층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1199,7 +1195,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wsvw5em</t>
+          <t>https://talk.naver.com/ct/wqbu4w7</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1213,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2707</v>
+        <v>2077</v>
       </c>
       <c r="Q8" t="n">
-        <v>338</v>
+        <v>140</v>
       </c>
       <c r="R8" t="n">
-        <v>3045</v>
+        <v>2217</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,17 +1224,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>38521265</t>
+          <t>1429668350</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38521265</t>
+          <t>https://m.place.naver.com/place/1429668350</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1250,34 +1246,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>스카이짐 24H &amp; 기구필라테스</t>
+          <t>에스에프짐 명지점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>skygym99@naver.com</t>
+          <t>sf_gym@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1484-5661</t>
+          <t>0507-1403-1474</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산 금정구 금강로 441 7층 8층 9층</t>
+          <t>부산 강서구 명지국제1로 60-1 10층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>http://www.skygym.co.kr</t>
+          <t>http://www.instagram.com/s.f_gym</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1287,7 +1283,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1297,7 +1293,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wl5mkqh</t>
+          <t>https://talk.naver.com/ct/w4574z</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1307,17 +1303,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2704</v>
+        <v>937</v>
       </c>
       <c r="Q9" t="n">
-        <v>116</v>
+        <v>545</v>
       </c>
       <c r="R9" t="n">
-        <v>2820</v>
+        <v>1482</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,17 +1322,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1730198934</t>
+          <t>1154395745</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1730198934</t>
+          <t>https://m.place.naver.com/place/1154395745</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1348,34 +1344,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>빅스짐 하단점 헬스 PT</t>
+          <t>스카이짐 24H &amp; 기구필라테스</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bigsgym20@naver.com</t>
+          <t>skygym99@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1357-6662</t>
+          <t>0507-1484-5661</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산 사하구 낙동대로457번길 5 301호</t>
+          <t>부산 금정구 금강로 441 7층 8층 9층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bigsgym_hadan</t>
+          <t>http://www.skygym.co.kr</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1385,7 +1381,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1395,7 +1391,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5v19w</t>
+          <t>https://talk.naver.com/ct/wl5mkqh</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1405,17 +1401,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1155</v>
+        <v>2707</v>
       </c>
       <c r="Q10" t="n">
-        <v>421</v>
+        <v>118</v>
       </c>
       <c r="R10" t="n">
-        <v>1576</v>
+        <v>2825</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,51 +1420,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1652983472</t>
+          <t>1730198934</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1652983472</t>
+          <t>https://m.place.naver.com/place/1730198934</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>멋짐 서면점</t>
+          <t>빅스짐 하단점 헬스 PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>mutgym8689@naver.com</t>
+          <t>bigsgym20@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1314-8689</t>
+          <t>0507-1357-6662</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>부산 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
+          <t>부산 사하구 낙동대로457번길 5 301호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mutgym8689</t>
+          <t>https://www.instagram.com/bigsgym_hadan</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1483,7 +1479,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1493,7 +1489,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4h77f</t>
+          <t>https://talk.naver.com/ct/w5v19w</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1507,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1413</v>
+        <v>1155</v>
       </c>
       <c r="Q11" t="n">
-        <v>1048</v>
+        <v>429</v>
       </c>
       <c r="R11" t="n">
-        <v>2461</v>
+        <v>1584</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1522,51 +1518,51 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1024587035</t>
+          <t>1652983472</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1024587035</t>
+          <t>https://m.place.naver.com/place/1652983472</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>멋짐 서면2호점</t>
+          <t>판테온짐 국제점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>mutgym_@naver.com</t>
+          <t>phantheon2@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1378-8691</t>
+          <t>0507-1312-1141</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>부산 부산진구 중앙대로666번길 50 201동 지하2층 5-13호</t>
+          <t>부산 강서구 명지국제6로1번길 30 A동 4층-필라테스&amp;G.X, 5층-헬스</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mutgym_seomyeon_2</t>
+          <t>https://blog.naver.com/phantheon2</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1581,7 +1577,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1591,7 +1587,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wm5u9og</t>
+          <t>https://talk.naver.com/ct/w9jio99</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1605,13 +1601,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>517</v>
+        <v>82</v>
       </c>
       <c r="Q12" t="n">
-        <v>400</v>
+        <v>23</v>
       </c>
       <c r="R12" t="n">
-        <v>917</v>
+        <v>105</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1620,17 +1616,115 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2036420985</t>
+          <t>2076801787</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2036420985</t>
+          <t>https://m.place.naver.com/place/2076801787</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>멋짐 서면점</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>mutgym8689@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1314-8689</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>부산 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/mutgym8689</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4h77f</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>1436</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1054</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2490</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1024587035</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1024587035</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/부산_헬스장.xlsx
+++ b/naver-place-crawler/results_health/부산_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -427,7 +427,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="41" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>일레븐핏 부산대점</t>
+          <t>피트니스스퀘어 헬스&amp;PT&amp;기구필라테스 서면점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>elevenfit@naver.com</t>
+          <t>fmpt__teddy@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1495-7982</t>
+          <t>0507-1343-6817</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산 금정구 금강로 209 한신시티빌 B1F</t>
+          <t>부산 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/elevenfit</t>
+          <t>https://open.kakao.com/o/sksoe31e</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -611,12 +611,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w9y42eh</t>
+          <t>https://talk.naver.com/ct/w4fpwi</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>134</v>
+        <v>1092</v>
       </c>
       <c r="Q2" t="n">
-        <v>750</v>
+        <v>845</v>
       </c>
       <c r="R2" t="n">
-        <v>884</v>
+        <v>1937</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,51 +640,51 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1356064248</t>
+          <t>1138689357</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1356064248</t>
+          <t>https://m.place.naver.com/place/1138689357</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>피트니스스퀘어 헬스&amp;PT&amp;기구필라테스 서면점</t>
+          <t>윤피티앤짐</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>fmpt__teddy@naver.com</t>
+          <t>yunpt-gym@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1343-6817</t>
+          <t>0507-1391-9943</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
+          <t>부산 금정구 부산대학로49번길 33-3 1층 좌측</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sksoe31e</t>
+          <t>https://blog.naver.com/yunpt-gym</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -709,27 +709,27 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4fpwi</t>
+          <t>https://talk.naver.com/ct/wpgkdoj</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1089</v>
+        <v>50</v>
       </c>
       <c r="Q3" t="n">
-        <v>838</v>
+        <v>43</v>
       </c>
       <c r="R3" t="n">
-        <v>1927</v>
+        <v>93</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,17 +738,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1138689357</t>
+          <t>1010289296</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1138689357</t>
+          <t>https://m.place.naver.com/place/1010289296</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -760,34 +760,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>플로우휘트니스 명지오션시티점</t>
+          <t>하이어짐 트레이닝 센터</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>j1024up@naver.com</t>
+          <t>q4142@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1491-2401</t>
+          <t>051-622-4259</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산 강서구 명지오션시티4로 90 6층 601호</t>
+          <t>부산 남구 분포로 113 메트로시티 주2상가, 5층 505호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://naver.me/5ISWRulS</t>
+          <t>https://blog.naver.com/q4142</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -797,15 +797,19 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4qs85</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -813,17 +817,17 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="Q4" t="n">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="R4" t="n">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,17 +836,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1677475057</t>
+          <t>1953938203</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1677475057</t>
+          <t>https://m.place.naver.com/place/1953938203</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -915,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="Q5" t="n">
         <v>1520</v>
       </c>
       <c r="R5" t="n">
-        <v>2942</v>
+        <v>2940</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -940,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1013,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1456</v>
+        <v>1458</v>
       </c>
       <c r="Q6" t="n">
-        <v>1825</v>
+        <v>1827</v>
       </c>
       <c r="R6" t="n">
-        <v>3281</v>
+        <v>3285</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1038,7 +1042,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1111,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2883</v>
+        <v>2889</v>
       </c>
       <c r="Q7" t="n">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="R7" t="n">
-        <v>3783</v>
+        <v>3790</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1136,7 +1140,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1209,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2077</v>
+        <v>2079</v>
       </c>
       <c r="Q8" t="n">
         <v>140</v>
       </c>
       <c r="R8" t="n">
-        <v>2217</v>
+        <v>2219</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1234,7 +1238,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1246,29 +1250,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>에스에프짐 명지점</t>
+          <t>커스텀피트니스 사직점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>sf_gym@naver.com</t>
+          <t>customfitness3@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1403-1474</t>
+          <t>0507-1411-0779</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산 강서구 명지국제1로 60-1 10층</t>
+          <t>부산 동래구 사직북로 4 지하 1층 커스텀피트니스 사직점</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/s.f_gym</t>
+          <t>https://www.instagram.com/customfitness_sajik/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1293,7 +1297,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4574z</t>
+          <t>https://talk.naver.com/ct/w4uy7l</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1307,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>937</v>
+        <v>590</v>
       </c>
       <c r="Q9" t="n">
-        <v>545</v>
+        <v>263</v>
       </c>
       <c r="R9" t="n">
-        <v>1482</v>
+        <v>853</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,17 +1326,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1154395745</t>
+          <t>1290468945</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1154395745</t>
+          <t>https://m.place.naver.com/place/1290468945</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1344,34 +1348,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>스카이짐 24H &amp; 기구필라테스</t>
+          <t>에스에프짐 명지점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>skygym99@naver.com</t>
+          <t>sf_gym@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1484-5661</t>
+          <t>0507-1403-1474</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산 금정구 금강로 441 7층 8층 9층</t>
+          <t>부산 강서구 명지국제1로 60-1 10층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>http://www.skygym.co.kr</t>
+          <t>http://www.instagram.com/s.f_gym</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1381,7 +1385,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1391,7 +1395,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wl5mkqh</t>
+          <t>https://talk.naver.com/ct/w4574z</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1401,17 +1405,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2707</v>
+        <v>941</v>
       </c>
       <c r="Q10" t="n">
-        <v>118</v>
+        <v>545</v>
       </c>
       <c r="R10" t="n">
-        <v>2825</v>
+        <v>1486</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,51 +1424,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1730198934</t>
+          <t>1154395745</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1730198934</t>
+          <t>https://m.place.naver.com/place/1154395745</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>빅스짐 하단점 헬스 PT</t>
+          <t>멋짐 서면점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>bigsgym20@naver.com</t>
+          <t>mutgym8689@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1357-6662</t>
+          <t>0507-1314-8689</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>부산 사하구 낙동대로457번길 5 301호</t>
+          <t>부산 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bigsgym_hadan</t>
+          <t>https://blog.naver.com/mutgym8689</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1479,7 +1483,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1489,7 +1493,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5v19w</t>
+          <t>https://talk.naver.com/ct/w4h77f</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1503,13 +1507,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1155</v>
+        <v>1441</v>
       </c>
       <c r="Q11" t="n">
-        <v>429</v>
+        <v>1056</v>
       </c>
       <c r="R11" t="n">
-        <v>1584</v>
+        <v>2497</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1518,213 +1522,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1652983472</t>
+          <t>1024587035</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1652983472</t>
+          <t>https://m.place.naver.com/place/1024587035</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>판테온짐 국제점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>phantheon2@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1312-1141</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>부산 강서구 명지국제6로1번길 30 A동 4층-필라테스&amp;G.X, 5층-헬스</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/phantheon2</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w9jio99</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>82</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>23</v>
-      </c>
-      <c r="R12" t="n">
-        <v>105</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>2076801787</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2076801787</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>멋짐 서면점</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>mutgym8689@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1314-8689</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>부산 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/mutgym8689</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4h77f</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>1436</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1054</v>
-      </c>
-      <c r="R13" t="n">
-        <v>2490</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1024587035</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1024587035</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/부산_헬스장.xlsx
+++ b/naver-place-crawler/results_health/부산_헬스장.xlsx
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>피트니스스퀘어 헬스&amp;PT&amp;기구필라테스 서면점</t>
+          <t>일레븐핏 부산대점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>fmpt__teddy@naver.com</t>
+          <t>elevenfit@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1343-6817</t>
+          <t>0507-1495-7982</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
+          <t>부산 금정구 금강로 209 한신시티빌 B1F</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sksoe31e</t>
+          <t>https://blog.naver.com/elevenfit</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -611,12 +611,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4fpwi</t>
+          <t>https://talk.naver.com/ct/w9y42eh</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1092</v>
+        <v>134</v>
       </c>
       <c r="Q2" t="n">
-        <v>845</v>
+        <v>751</v>
       </c>
       <c r="R2" t="n">
-        <v>1937</v>
+        <v>885</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1138689357</t>
+          <t>1356064248</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1138689357</t>
+          <t>https://m.place.naver.com/place/1356064248</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -657,34 +657,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>윤피티앤짐</t>
+          <t>피트니스스퀘어 헬스&amp;PT&amp;기구필라테스 서면점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>yunpt-gym@naver.com</t>
+          <t>fmpt__teddy@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1391-9943</t>
+          <t>0507-1343-6817</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산 금정구 부산대학로49번길 33-3 1층 좌측</t>
+          <t>부산 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/yunpt-gym</t>
+          <t>https://open.kakao.com/o/sksoe31e</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -709,27 +709,27 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wpgkdoj</t>
+          <t>https://talk.naver.com/ct/w4fpwi</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>50</v>
+        <v>1092</v>
       </c>
       <c r="Q3" t="n">
-        <v>43</v>
+        <v>847</v>
       </c>
       <c r="R3" t="n">
-        <v>93</v>
+        <v>1939</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1010289296</t>
+          <t>1138689357</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1010289296</t>
+          <t>https://m.place.naver.com/place/1138689357</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -760,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>하이어짐 트레이닝 센터</t>
+          <t>윤피티앤짐</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q4142@naver.com</t>
+          <t>yunpt-gym@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>051-622-4259</t>
+          <t>0507-1391-9943</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산 남구 분포로 113 메트로시티 주2상가, 5층 505호</t>
+          <t>부산 금정구 부산대학로49번길 33-3 1층 좌측</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/q4142</t>
+          <t>https://blog.naver.com/yunpt-gym</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4qs85</t>
+          <t>https://talk.naver.com/ct/wpgkdoj</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -817,17 +817,17 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="Q4" t="n">
-        <v>252</v>
+        <v>43</v>
       </c>
       <c r="R4" t="n">
-        <v>299</v>
+        <v>93</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1953938203</t>
+          <t>1010289296</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1953938203</t>
+          <t>https://m.place.naver.com/place/1010289296</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">

--- a/naver-place-crawler/results_health/부산_헬스장.xlsx
+++ b/naver-place-crawler/results_health/부산_헬스장.xlsx
@@ -417,12 +417,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>일레븐핏 부산대점</t>
+          <t>피트니스스퀘어 헬스&amp;PT&amp;기구필라테스 서면점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>elevenfit@naver.com</t>
+          <t>fmpt__teddy@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1495-7982</t>
+          <t>0507-1343-6817</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산 금정구 금강로 209 한신시티빌 B1F</t>
+          <t>부산 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/elevenfit</t>
+          <t>https://open.kakao.com/o/sksoe31e</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -611,12 +611,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w9y42eh</t>
+          <t>https://talk.naver.com/ct/w4fpwi</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>134</v>
+        <v>1093</v>
       </c>
       <c r="Q2" t="n">
-        <v>751</v>
+        <v>847</v>
       </c>
       <c r="R2" t="n">
-        <v>885</v>
+        <v>1940</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +640,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1356064248</t>
+          <t>1138689357</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1356064248</t>
+          <t>https://m.place.naver.com/place/1138689357</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -854,29 +854,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>피트니스스퀘어 헬스&amp;PT&amp;기구필라테스 서면점</t>
+          <t>멋짐 헬스&amp;PT 연산점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>fmpt__teddy@naver.com</t>
+          <t>mutgym8689@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1343-6817</t>
+          <t>0507-1409-8689</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
+          <t>부산 연제구 반송로 21 5층,6층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sksoe31e</t>
+          <t>https://blog.naver.com/mutgym8689</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4fpwi</t>
+          <t>https://talk.naver.com/ct/w4pm77</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -915,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1093</v>
+        <v>1420</v>
       </c>
       <c r="Q5" t="n">
-        <v>847</v>
+        <v>1520</v>
       </c>
       <c r="R5" t="n">
-        <v>1940</v>
+        <v>2940</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,51 +930,51 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1138689357</t>
+          <t>1868714041</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1138689357</t>
+          <t>https://m.place.naver.com/place/1868714041</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>멋짐 헬스&amp;PT 연산점</t>
+          <t>건담짐 미국감성프리미엄헬스&amp;PT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mutgym8689@naver.com</t>
+          <t>rlarjsdn12433@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1409-8689</t>
+          <t>0507-1323-5243</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산 연제구 반송로 21 5층,6층</t>
+          <t>부산 동래구 온천천로 391 1층 건담짐</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mutgym8689</t>
+          <t>https://blog.naver.com/rlarjsdn12433</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4pm77</t>
+          <t>https://talk.naver.com/ct/w44x8o</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1013,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1420</v>
+        <v>2890</v>
       </c>
       <c r="Q6" t="n">
-        <v>1520</v>
+        <v>901</v>
       </c>
       <c r="R6" t="n">
-        <v>2940</v>
+        <v>3791</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,51 +1028,51 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1868714041</t>
+          <t>1130935293</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1868714041</t>
+          <t>https://m.place.naver.com/place/1130935293</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>건담짐 미국감성프리미엄헬스&amp;PT</t>
+          <t>멋짐 헬스&amp;PT 동래점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>rlarjsdn12433@naver.com</t>
+          <t>mutgym8689@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1323-5243</t>
+          <t>0507-1355-8689</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산 동래구 온천천로 391 1층 건담짐</t>
+          <t>부산 동래구 명륜로103번길 8 스카이뷰 4층, 5층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rlarjsdn12433</t>
+          <t>https://blog.naver.com/mutgym8689</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w44x8o</t>
+          <t>https://talk.naver.com/ct/w4pm7n</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2890</v>
+        <v>1614</v>
       </c>
       <c r="Q7" t="n">
-        <v>901</v>
+        <v>1750</v>
       </c>
       <c r="R7" t="n">
-        <v>3791</v>
+        <v>3364</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,56 +1126,56 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1130935293</t>
+          <t>1261115217</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1130935293</t>
+          <t>https://m.place.naver.com/place/1261115217</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>멋짐 헬스&amp;PT 동래점</t>
+          <t>스카이짐24H &amp; 기구필라테스 &amp; GDR골프</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>mutgym8689@naver.com</t>
+          <t>skygym21@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1355-8689</t>
+          <t>0507-1473-5661</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산 동래구 명륜로103번길 8 스카이뷰 4층, 5층</t>
+          <t>부산 사하구 장평로 440 5층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mutgym8689</t>
+          <t>http://www.skygym.co.kr</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4pm7n</t>
+          <t>https://talk.naver.com/ct/wqbu4w7</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1205,17 +1205,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1614</v>
+        <v>2079</v>
       </c>
       <c r="Q8" t="n">
-        <v>1750</v>
+        <v>140</v>
       </c>
       <c r="R8" t="n">
-        <v>3364</v>
+        <v>2219</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,17 +1224,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1261115217</t>
+          <t>1429668350</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1261115217</t>
+          <t>https://m.place.naver.com/place/1429668350</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1246,44 +1246,44 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>스카이짐24H &amp; 기구필라테스 &amp; GDR골프</t>
+          <t>커스텀피트니스 사직점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>skygym21@naver.com</t>
+          <t>customfitness3@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1473-5661</t>
+          <t>0507-1411-0779</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산 사하구 장평로 440 5층</t>
+          <t>부산 동래구 사직북로 4 지하 1층 커스텀피트니스 사직점</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>http://www.skygym.co.kr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wqbu4w7</t>
+          <t>https://talk.naver.com/ct/w4uy7l</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1303,17 +1303,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2079</v>
+        <v>594</v>
       </c>
       <c r="Q9" t="n">
-        <v>140</v>
+        <v>264</v>
       </c>
       <c r="R9" t="n">
-        <v>2219</v>
+        <v>858</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,17 +1322,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1429668350</t>
+          <t>1290468945</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1429668350</t>
+          <t>https://m.place.naver.com/place/1290468945</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1344,44 +1344,44 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>스카이짐 24H &amp; 기구필라테스</t>
+          <t>에스에프짐 명지점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>skygym99@naver.com</t>
+          <t>sf_gym@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1484-5661</t>
+          <t>0507-1403-1474</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산 금정구 금강로 441 7층 8층 9층</t>
+          <t>부산 강서구 명지국제1로 60-1 10층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>http://www.skygym.co.kr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wl5mkqh</t>
+          <t>https://talk.naver.com/ct/w4574z</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1401,17 +1401,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2708</v>
+        <v>941</v>
       </c>
       <c r="Q10" t="n">
-        <v>118</v>
+        <v>545</v>
       </c>
       <c r="R10" t="n">
-        <v>2826</v>
+        <v>1486</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,115 +1420,311 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1730198934</t>
+          <t>1154395745</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1730198934</t>
+          <t>https://m.place.naver.com/place/1154395745</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>멋짐 서면점</t>
+          <t>스카이짐 24H &amp; 기구필라테스</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>mutgym8689@naver.com</t>
+          <t>skygym99@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1314-8689</t>
+          <t>0507-1484-5661</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
+          <t>부산 금정구 금강로 441 7층 8층 9층</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>http://www.skygym.co.kr</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wl5mkqh</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>2708</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>118</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2826</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1730198934</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1730198934</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>빅스짐 하단점 헬스 PT</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>bigsgym20@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1357-6662</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>부산 사하구 낙동대로457번길 5 301호</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5v19w</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>1154</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>431</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1585</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1652983472</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1652983472</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>멋짐 서면점</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>mutgym8689@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1314-8689</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
           <t>부산 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>https://blog.naver.com/mutgym8689</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t>https://talk.naver.com/ct/w4h77f</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
         <v>1441</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q13" t="n">
         <v>1056</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R13" t="n">
         <v>2497</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
         <is>
           <t>1024587035</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1024587035</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/부산_헬스장.xlsx
+++ b/naver-place-crawler/results_health/부산_헬스장.xlsx
@@ -422,7 +422,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>일레븐핏 부산대점</t>
+          <t>피트니스스퀘어 헬스&amp;PT&amp;기구필라테스 서면점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>elevenfit@naver.com</t>
+          <t>fmpt__teddy@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1495-7982</t>
+          <t>0507-1343-6817</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산 금정구 금강로 209 한신시티빌 B1F</t>
+          <t>부산 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/elevenfit</t>
+          <t>https://open.kakao.com/o/sksoe31e</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -611,12 +611,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w9y42eh</t>
+          <t>https://talk.naver.com/ct/w4fpwi</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>134</v>
+        <v>1092</v>
       </c>
       <c r="Q2" t="n">
-        <v>751</v>
+        <v>849</v>
       </c>
       <c r="R2" t="n">
-        <v>885</v>
+        <v>1941</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +640,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1356064248</t>
+          <t>1138689357</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1356064248</t>
+          <t>https://m.place.naver.com/place/1138689357</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -842,46 +842,46 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>피트니스스퀘어 헬스&amp;PT&amp;기구필라테스 서면점</t>
+          <t>멋짐 서면점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>fmpt__teddy@naver.com</t>
+          <t>mutgym8689@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1343-6817</t>
+          <t>0507-1314-8689</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
+          <t>부산 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sksoe31e</t>
+          <t>https://blog.naver.com/mutgym8689</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4fpwi</t>
+          <t>https://talk.naver.com/ct/w4h77f</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -915,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1092</v>
+        <v>1448</v>
       </c>
       <c r="Q5" t="n">
-        <v>849</v>
+        <v>1057</v>
       </c>
       <c r="R5" t="n">
-        <v>1941</v>
+        <v>2505</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,17 +930,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1138689357</t>
+          <t>1024587035</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1138689357</t>
+          <t>https://m.place.naver.com/place/1024587035</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1246,34 +1246,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>스카이짐24H &amp; 기구필라테스 &amp; GDR골프</t>
+          <t>커스텀피트니스 사직점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>skygym21@naver.com</t>
+          <t>customfitness3@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1473-5661</t>
+          <t>0507-1411-0779</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산 사하구 장평로 440 5층</t>
+          <t>부산 동래구 사직북로 4 지하 1층 커스텀피트니스 사직점</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>http://www.skygym.co.kr</t>
+          <t>https://www.instagram.com/customfitness_sajik/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wqbu4w7</t>
+          <t>https://talk.naver.com/ct/w4uy7l</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1303,17 +1303,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2079</v>
+        <v>594</v>
       </c>
       <c r="Q9" t="n">
-        <v>141</v>
+        <v>264</v>
       </c>
       <c r="R9" t="n">
-        <v>2220</v>
+        <v>858</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,17 +1322,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1429668350</t>
+          <t>1290468945</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1429668350</t>
+          <t>https://m.place.naver.com/place/1290468945</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1344,34 +1344,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>스카이짐 24H &amp; 기구필라테스</t>
+          <t>에스에프짐 명지점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>skygym99@naver.com</t>
+          <t>sf_gym@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1484-5661</t>
+          <t>0507-1403-1474</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산 금정구 금강로 441 7층 8층 9층</t>
+          <t>부산 강서구 명지국제1로 60-1 10층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>http://www.skygym.co.kr</t>
+          <t>http://www.instagram.com/s.f_gym</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wl5mkqh</t>
+          <t>https://talk.naver.com/ct/w4574z</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1401,17 +1401,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2710</v>
+        <v>945</v>
       </c>
       <c r="Q10" t="n">
-        <v>119</v>
+        <v>545</v>
       </c>
       <c r="R10" t="n">
-        <v>2829</v>
+        <v>1490</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,51 +1420,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1730198934</t>
+          <t>1154395745</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1730198934</t>
+          <t>https://m.place.naver.com/place/1154395745</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>빅스짐 하단점 헬스 PT</t>
+          <t>노블짐 PT&amp;헬스</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>bigsgym20@naver.com</t>
+          <t>koreakorea7754@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1357-6662</t>
+          <t>0507-1495-9017</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>부산 사하구 낙동대로457번길 5 301호</t>
+          <t>부산 남구 용호로 187-2 노블짐 3층 전체</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bigsgym_hadan</t>
+          <t>https://blog.naver.com/koreakorea7754</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5v19w</t>
+          <t>https://talk.naver.com/ct/w451sf</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1503,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1152</v>
+        <v>294</v>
       </c>
       <c r="Q11" t="n">
-        <v>432</v>
+        <v>394</v>
       </c>
       <c r="R11" t="n">
-        <v>1584</v>
+        <v>688</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1518,51 +1518,51 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1652983472</t>
+          <t>1231483955</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1652983472</t>
+          <t>https://m.place.naver.com/place/1231483955</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>멋짐 서면점</t>
+          <t>빅스짐 하단점 헬스 PT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>mutgym8689@naver.com</t>
+          <t>bigsgym20@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1314-8689</t>
+          <t>0507-1357-6662</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>부산 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
+          <t>부산 사하구 낙동대로457번길 5 301호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mutgym8689</t>
+          <t>https://www.instagram.com/bigsgym_hadan</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4h77f</t>
+          <t>https://talk.naver.com/ct/w5v19w</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1601,13 +1601,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1446</v>
+        <v>1152</v>
       </c>
       <c r="Q12" t="n">
-        <v>1057</v>
+        <v>433</v>
       </c>
       <c r="R12" t="n">
-        <v>2503</v>
+        <v>1585</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1616,17 +1616,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1024587035</t>
+          <t>1652983472</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1024587035</t>
+          <t>https://m.place.naver.com/place/1652983472</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/부산_헬스장.xlsx
+++ b/naver-place-crawler/results_health/부산_헬스장.xlsx
@@ -422,7 +422,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -662,34 +662,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>플로우휘트니스 명지오션시티점</t>
+          <t>일레븐핏 부산대점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>j1024up@naver.com</t>
+          <t>elevenfit@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1491-2401</t>
+          <t>0507-1495-7982</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산 강서구 명지오션시티4로 90 6층 601호</t>
+          <t>부산 금정구 금강로 209 한신시티빌 B1F</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://naver.me/5ISWRulS</t>
+          <t>https://blog.naver.com/elevenfit</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -699,15 +699,19 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w9y42eh</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -715,17 +719,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>42</v>
+        <v>134</v>
       </c>
       <c r="Q3" t="n">
-        <v>258</v>
+        <v>751</v>
       </c>
       <c r="R3" t="n">
-        <v>300</v>
+        <v>885</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1677475057</t>
+          <t>1356064248</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1677475057</t>
+          <t>https://m.place.naver.com/place/1356064248</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -756,34 +760,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>미라클짐 헬스&amp;PT 필라테스 학장점</t>
+          <t>플로우휘트니스 명지오션시티점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>miraclegym2@naver.com</t>
+          <t>j1024up@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>051-313-7705</t>
+          <t>0507-1491-2401</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산 사상구 대동로 95 3층 미라클짐 학장점</t>
+          <t>부산 강서구 명지오션시티4로 90 6층 601호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/miracle__gym?igsh=YXp2czJxNmdiMjA0&amp;utm_source=qr</t>
+          <t>https://naver.me/5ISWRulS</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -798,14 +802,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4iq5a</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -813,17 +813,17 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>120</v>
+        <v>42</v>
       </c>
       <c r="Q4" t="n">
-        <v>146</v>
+        <v>258</v>
       </c>
       <c r="R4" t="n">
-        <v>266</v>
+        <v>300</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,12 +832,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1169221564</t>
+          <t>1677475057</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1169221564</t>
+          <t>https://m.place.naver.com/place/1677475057</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -854,29 +854,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>멋짐 서면점</t>
+          <t>미라클짐 헬스&amp;PT 필라테스 학장점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>mutgym8689@naver.com</t>
+          <t>miraclegym2@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1314-8689</t>
+          <t>051-313-7705</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
+          <t>부산 사상구 대동로 95 3층 미라클짐 학장점</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mutgym8689</t>
+          <t>https://www.instagram.com/miracle__gym?igsh=YXp2czJxNmdiMjA0&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4h77f</t>
+          <t>https://talk.naver.com/ct/w4iq5a</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -915,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1448</v>
+        <v>120</v>
       </c>
       <c r="Q5" t="n">
-        <v>1057</v>
+        <v>146</v>
       </c>
       <c r="R5" t="n">
-        <v>2505</v>
+        <v>266</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,12 +930,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1024587035</t>
+          <t>1169221564</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1024587035</t>
+          <t>https://m.place.naver.com/place/1169221564</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -947,12 +947,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>멋짐 헬스&amp;PT 연산점</t>
+          <t>멋짐 서면점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -963,13 +963,13 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1409-8689</t>
+          <t>0507-1314-8689</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산 연제구 반송로 21 5층,6층</t>
+          <t>부산 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4pm77</t>
+          <t>https://talk.naver.com/ct/w4h77f</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1013,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1423</v>
+        <v>1448</v>
       </c>
       <c r="Q6" t="n">
-        <v>1521</v>
+        <v>1057</v>
       </c>
       <c r="R6" t="n">
-        <v>2944</v>
+        <v>2505</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,12 +1028,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1868714041</t>
+          <t>1024587035</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1868714041</t>
+          <t>https://m.place.naver.com/place/1024587035</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1045,34 +1045,34 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>건담짐 미국감성프리미엄헬스&amp;PT</t>
+          <t>멋짐 헬스&amp;PT 연산점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>rlarjsdn12433@naver.com</t>
+          <t>mutgym8689@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1323-5243</t>
+          <t>0507-1409-8689</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산 동래구 온천천로 391 1층 건담짐</t>
+          <t>부산 연제구 반송로 21 5층,6층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rlarjsdn12433</t>
+          <t>https://blog.naver.com/mutgym8689</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w44x8o</t>
+          <t>https://talk.naver.com/ct/w4pm77</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2895</v>
+        <v>1423</v>
       </c>
       <c r="Q7" t="n">
-        <v>901</v>
+        <v>1521</v>
       </c>
       <c r="R7" t="n">
-        <v>3796</v>
+        <v>2944</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,12 +1126,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1130935293</t>
+          <t>1868714041</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1130935293</t>
+          <t>https://m.place.naver.com/place/1868714041</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1148,29 +1148,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>빔스짐</t>
+          <t>건담짐 미국감성프리미엄헬스&amp;PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>vimsgym_3@naver.com</t>
+          <t>rlarjsdn12433@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1310-1516</t>
+          <t>0507-1323-5243</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산 해운대구 선수촌로 95 지하1층</t>
+          <t>부산 동래구 온천천로 391 1층 건담짐</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/vims_gym_3</t>
+          <t>https://blog.naver.com/rlarjsdn12433</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wco57td</t>
+          <t>https://talk.naver.com/ct/w44x8o</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>597</v>
+        <v>2895</v>
       </c>
       <c r="Q8" t="n">
-        <v>68</v>
+        <v>901</v>
       </c>
       <c r="R8" t="n">
-        <v>665</v>
+        <v>3796</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1097711832</t>
+          <t>1130935293</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1097711832</t>
+          <t>https://m.place.naver.com/place/1130935293</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1246,29 +1246,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>커스텀피트니스 사직점</t>
+          <t>빔스짐</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>customfitness3@naver.com</t>
+          <t>vimsgym_3@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1411-0779</t>
+          <t>0507-1310-1516</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산 동래구 사직북로 4 지하 1층 커스텀피트니스 사직점</t>
+          <t>부산 해운대구 선수촌로 95 지하1층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/customfitness_sajik/</t>
+          <t>https://www.instagram.com/vims_gym_3</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4uy7l</t>
+          <t>https://talk.naver.com/ct/wco57td</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1307,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="Q9" t="n">
-        <v>264</v>
+        <v>68</v>
       </c>
       <c r="R9" t="n">
-        <v>858</v>
+        <v>665</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1290468945</t>
+          <t>1097711832</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1290468945</t>
+          <t>https://m.place.naver.com/place/1097711832</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1437,34 +1437,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>노블짐 PT&amp;헬스</t>
+          <t>빅스짐 하단점 헬스 PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>koreakorea7754@naver.com</t>
+          <t>bigsgym20@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1495-9017</t>
+          <t>0507-1357-6662</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>부산 남구 용호로 187-2 노블짐 3층 전체</t>
+          <t>부산 사하구 낙동대로457번길 5 301호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/koreakorea7754</t>
+          <t>https://www.instagram.com/bigsgym_hadan</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w451sf</t>
+          <t>https://talk.naver.com/ct/w5v19w</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1503,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>294</v>
+        <v>1152</v>
       </c>
       <c r="Q11" t="n">
-        <v>394</v>
+        <v>433</v>
       </c>
       <c r="R11" t="n">
-        <v>688</v>
+        <v>1585</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1518,12 +1518,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1231483955</t>
+          <t>1652983472</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1231483955</t>
+          <t>https://m.place.naver.com/place/1652983472</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1535,34 +1535,34 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>빅스짐 하단점 헬스 PT</t>
+          <t>언로드 PT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>bigsgym20@naver.com</t>
+          <t>unloadpt@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1357-6662</t>
+          <t>0507-1320-4232</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>부산 사하구 낙동대로457번길 5 301호</t>
+          <t>부산 해운대구 우동1로20번길 27-10 3층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bigsgym_hadan</t>
+          <t>https://open.kakao.com/o/s8bzzHmi</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1587,12 +1587,12 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5v19w</t>
+          <t>https://talk.naver.com/ct/wzjd0hu</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1601,13 +1601,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1152</v>
+        <v>4</v>
       </c>
       <c r="Q12" t="n">
-        <v>433</v>
+        <v>2</v>
       </c>
       <c r="R12" t="n">
-        <v>1585</v>
+        <v>6</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1616,12 +1616,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1652983472</t>
+          <t>2024136684</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1652983472</t>
+          <t>https://m.place.naver.com/place/2024136684</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
